--- a/志工名冊.xlsx
+++ b/志工名冊.xlsx
@@ -14813,5 +14813,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>